--- a/data/trans_orig/KIDMED_R3-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/KIDMED_R3-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>36513</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>30746</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>42185</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>67,98%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>57,24%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>78,54%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>29258</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19047</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>36848</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>54,48%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>35,47%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>68,62%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>38099</t>
+          <t>28905</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29151</t>
+          <t>23906</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44120</t>
+          <t>34382</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>67356</t>
+          <t>65418</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53030</t>
+          <t>57366</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77021</t>
+          <t>73788</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>74,07%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17202</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11530</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22969</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>32,02%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>21,46%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>42,76%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>24441</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>16851</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>34652</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>45,52%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>31,38%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>64,53%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20246</t>
+          <t>17000</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14225</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29194</t>
+          <t>21999</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>44687</t>
+          <t>34202</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35022</t>
+          <t>25832</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59013</t>
+          <t>42254</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>42,42%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>296099</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>272031</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>316961</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>63,48%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>58,32%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>67,96%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>400</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>269758</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>213552</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>293303</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>59,7%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>47,26%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>64,91%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>314792</t>
+          <t>268959</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>285979</t>
+          <t>251339</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>338106</t>
+          <t>284565</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>584550</t>
+          <t>565059</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>525318</t>
+          <t>536532</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>619729</t>
+          <t>590245</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>66,24%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>170324</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>149462</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>194392</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>36,52%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>32,04%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>41,68%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>182074</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>158529</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>238280</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>40,3%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>35,09%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>52,74%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>190458</t>
+          <t>155707</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>167144</t>
+          <t>140101</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>219271</t>
+          <t>173327</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>372532</t>
+          <t>326031</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>337353</t>
+          <t>300845</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>431764</t>
+          <t>354558</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>39,79%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>625</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>106411</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>95211</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>116467</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>63,84%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>57,12%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>69,87%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>93581</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>82758</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>102150</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>64,02%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>56,61%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>69,88%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>113226</t>
+          <t>95279</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>100565</t>
+          <t>84844</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>125650</t>
+          <t>104672</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>206806</t>
+          <t>201689</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>190799</t>
+          <t>186882</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>222083</t>
+          <t>215765</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>68,75%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>60275</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>50219</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>71475</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>36,16%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>30,13%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>42,88%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>52605</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>44036</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>63428</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>35,98%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>30,12%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>43,39%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>67913</t>
+          <t>51861</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55489</t>
+          <t>42468</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>80574</t>
+          <t>62296</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>120518</t>
+          <t>112136</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>105241</t>
+          <t>98060</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>136525</t>
+          <t>126943</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>40,45%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>439023</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>411473</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>463185</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>63,92%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>59,91%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>67,44%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>584</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>392597</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>342604</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>420711</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>60,24%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>52,57%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>64,55%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>466116</t>
+          <t>393143</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>435981</t>
+          <t>371438</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>495052</t>
+          <t>411937</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>858713</t>
+          <t>832165</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>803647</t>
+          <t>797550</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>896420</t>
+          <t>862427</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>66,11%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>247801</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>223639</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>275351</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>36,08%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>32,56%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>40,09%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>259120</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>231006</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>309113</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>39,76%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>35,45%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>47,43%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>278617</t>
+          <t>224568</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>249681</t>
+          <t>205774</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>308752</t>
+          <t>246273</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>537737</t>
+          <t>472370</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>500030</t>
+          <t>442108</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>592803</t>
+          <t>506985</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>38,86%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
